--- a/plate3d/PLATE3D_TOWER.xlsx
+++ b/plate3d/PLATE3D_TOWER.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2416" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2416" uniqueCount="328">
   <si>
     <t>Saddle-jib tower crane - 48.5 m jib, 47 m to the apex</t>
   </si>
@@ -749,9 +749,6 @@
   </si>
   <si>
     <t>sc.cch_2</t>
-  </si>
-  <si>
-    <t>bar.ch_1</t>
   </si>
   <si>
     <t>bar.cw_1</t>
@@ -1443,7 +1440,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -1484,7 +1481,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>20</v>
       </c>
@@ -1525,7 +1522,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>20</v>
       </c>
@@ -1566,7 +1563,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>23</v>
       </c>
@@ -1739,7 +1736,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>20</v>
       </c>
@@ -1759,7 +1756,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
@@ -1779,7 +1776,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>20</v>
       </c>
@@ -1799,7 +1796,7 @@
         <v>2885</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>20</v>
       </c>
@@ -1819,7 +1816,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>20</v>
       </c>
@@ -1839,7 +1836,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>20</v>
       </c>
@@ -1859,7 +1856,7 @@
         <v>4300</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>20</v>
       </c>
@@ -1879,7 +1876,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>41</v>
       </c>
@@ -1899,7 +1896,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>20</v>
       </c>
@@ -1919,7 +1916,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>20</v>
       </c>
@@ -1939,7 +1936,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>20</v>
       </c>
@@ -1959,7 +1956,7 @@
         <v>3300</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
@@ -1979,7 +1976,7 @@
         <v>2600</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>20</v>
       </c>
@@ -1999,7 +1996,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>20</v>
       </c>
@@ -2019,7 +2016,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>20</v>
       </c>
@@ -2039,7 +2036,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2059,7 +2056,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>51</v>
       </c>
@@ -2079,7 +2076,7 @@
         <v>26000</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>20</v>
       </c>
@@ -2099,7 +2096,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>20</v>
       </c>
@@ -2119,7 +2116,7 @@
         <v>26000</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>20</v>
       </c>
@@ -2139,7 +2136,7 @@
         <v>4800</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>20</v>
       </c>
@@ -2159,7 +2156,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>20</v>
       </c>
@@ -2179,7 +2176,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>20</v>
       </c>
@@ -2199,7 +2196,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>20</v>
       </c>
@@ -2219,7 +2216,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>20</v>
       </c>
@@ -2254,7 +2251,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>20</v>
       </c>
@@ -2283,7 +2280,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>20</v>
       </c>
@@ -2312,7 +2309,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>20</v>
       </c>
@@ -2338,7 +2335,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>20</v>
       </c>
@@ -2364,7 +2361,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>20</v>
       </c>
@@ -2393,7 +2390,7 @@
         <v>2600</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,7 +2419,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>20</v>
       </c>
@@ -2451,7 +2448,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>20</v>
       </c>
@@ -2486,7 +2483,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>20</v>
       </c>
@@ -2515,7 +2512,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>20</v>
       </c>
@@ -2550,7 +2547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>20</v>
       </c>
@@ -2585,7 +2582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>83</v>
       </c>
@@ -2614,7 +2611,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>20</v>
       </c>
@@ -2643,7 +2640,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>20</v>
       </c>
@@ -2672,7 +2669,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>20</v>
       </c>
@@ -2698,7 +2695,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>20</v>
       </c>
@@ -2727,7 +2724,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>20</v>
       </c>
@@ -2756,7 +2753,7 @@
         <v>2080</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>20</v>
       </c>
@@ -2785,7 +2782,7 @@
         <v>2180</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>20</v>
       </c>
@@ -2814,7 +2811,7 @@
         <v>2180</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>20</v>
       </c>
@@ -2843,7 +2840,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>20</v>
       </c>
@@ -2869,7 +2866,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>20</v>
       </c>
@@ -2904,7 +2901,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>20</v>
       </c>
@@ -2930,7 +2927,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>20</v>
       </c>
@@ -2965,7 +2962,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>20</v>
       </c>
@@ -2985,7 +2982,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>20</v>
       </c>
@@ -3005,7 +3002,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>20</v>
       </c>
@@ -3025,7 +3022,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3045,7 +3042,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>20</v>
       </c>
@@ -3065,7 +3062,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>20</v>
       </c>
@@ -3085,7 +3082,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>106</v>
       </c>
@@ -3114,7 +3111,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>20</v>
       </c>
@@ -3134,7 +3131,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>20</v>
       </c>
@@ -3154,7 +3151,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>20</v>
       </c>
@@ -3183,7 +3180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>20</v>
       </c>
@@ -3212,7 +3209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>20</v>
       </c>
@@ -3232,7 +3229,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>20</v>
       </c>
@@ -3252,7 +3249,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>20</v>
       </c>
@@ -3272,7 +3269,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>20</v>
       </c>
@@ -4084,7 +4081,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>20</v>
       </c>
@@ -4142,7 +4139,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>20</v>
       </c>
@@ -4790,7 +4787,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>20</v>
       </c>
@@ -5728,7 +5725,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>20</v>
       </c>
@@ -5786,7 +5783,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>20</v>
       </c>
@@ -6070,7 +6067,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>20</v>
       </c>
@@ -7618,7 +7615,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>20</v>
       </c>
@@ -8054,7 +8051,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
         <v>20</v>
       </c>
@@ -8552,7 +8549,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
         <v>20</v>
       </c>
@@ -8874,7 +8871,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
         <v>20</v>
       </c>
@@ -9119,7 +9116,7 @@
         <v>243</v>
       </c>
       <c r="D223" t="s">
-        <v>246</v>
+        <v>47</v>
       </c>
       <c r="E223" t="s">
         <v>20</v>
@@ -9163,7 +9160,7 @@
         <v>243</v>
       </c>
       <c r="D224" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E224" t="s">
         <v>20</v>
@@ -9207,7 +9204,7 @@
         <v>243</v>
       </c>
       <c r="D225" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E225" t="s">
         <v>20</v>
@@ -9251,7 +9248,7 @@
         <v>243</v>
       </c>
       <c r="D226" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E226" t="s">
         <v>20</v>
@@ -9295,7 +9292,7 @@
         <v>243</v>
       </c>
       <c r="D227" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E227" t="s">
         <v>20</v>
@@ -9328,7 +9325,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
         <v>20</v>
       </c>
@@ -9386,7 +9383,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
         <v>20</v>
       </c>
@@ -9432,7 +9429,7 @@
         <v>128</v>
       </c>
       <c r="C232" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D232" t="s">
         <v>86</v>
@@ -9514,7 +9511,7 @@
         <v>128</v>
       </c>
       <c r="C234" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D234" t="s">
         <v>60</v>
@@ -9550,7 +9547,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
         <v>20</v>
       </c>
@@ -9596,10 +9593,10 @@
         <v>128</v>
       </c>
       <c r="C236" t="s">
+        <v>250</v>
+      </c>
+      <c r="D236" t="s">
         <v>251</v>
-      </c>
-      <c r="D236" t="s">
-        <v>252</v>
       </c>
       <c r="E236" t="s">
         <v>27</v>
@@ -9614,7 +9611,7 @@
         <v>620</v>
       </c>
       <c r="I236" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J236" t="s">
         <v>20</v>
@@ -9634,10 +9631,10 @@
         <v>128</v>
       </c>
       <c r="C237" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D237" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E237" t="s">
         <v>27</v>
@@ -9652,7 +9649,7 @@
         <v>620</v>
       </c>
       <c r="I237" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J237" t="s">
         <v>20</v>
@@ -9672,7 +9669,7 @@
         <v>128</v>
       </c>
       <c r="C238" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D238" t="s">
         <v>88</v>
@@ -9690,7 +9687,7 @@
         <v>360</v>
       </c>
       <c r="I238" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J238" t="s">
         <v>20</v>
@@ -9754,10 +9751,10 @@
         <v>128</v>
       </c>
       <c r="C240" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D240" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E240" t="s">
         <v>20</v>
@@ -9798,10 +9795,10 @@
         <v>128</v>
       </c>
       <c r="C241" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D241" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E241" t="s">
         <v>20</v>
@@ -9842,10 +9839,10 @@
         <v>128</v>
       </c>
       <c r="C242" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D242" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E242" t="s">
         <v>20</v>
@@ -9886,10 +9883,10 @@
         <v>128</v>
       </c>
       <c r="C243" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D243" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E243" t="s">
         <v>20</v>
@@ -9930,10 +9927,10 @@
         <v>128</v>
       </c>
       <c r="C244" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D244" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E244" t="s">
         <v>20</v>
@@ -9974,10 +9971,10 @@
         <v>128</v>
       </c>
       <c r="C245" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D245" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E245" t="s">
         <v>20</v>
@@ -10018,10 +10015,10 @@
         <v>128</v>
       </c>
       <c r="C246" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D246" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E246" t="s">
         <v>20</v>
@@ -10062,10 +10059,10 @@
         <v>128</v>
       </c>
       <c r="C247" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D247" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E247" t="s">
         <v>20</v>
@@ -10106,10 +10103,10 @@
         <v>128</v>
       </c>
       <c r="C248" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D248" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E248" t="s">
         <v>20</v>
@@ -10150,10 +10147,10 @@
         <v>128</v>
       </c>
       <c r="C249" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D249" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E249" t="s">
         <v>20</v>
@@ -10194,10 +10191,10 @@
         <v>128</v>
       </c>
       <c r="C250" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D250" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E250" t="s">
         <v>20</v>
@@ -10238,10 +10235,10 @@
         <v>128</v>
       </c>
       <c r="C251" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D251" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E251" t="s">
         <v>20</v>
@@ -10274,7 +10271,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="252" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
         <v>20</v>
       </c>
@@ -10320,7 +10317,7 @@
         <v>128</v>
       </c>
       <c r="C253" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D253" t="s">
         <v>152</v>
@@ -10332,7 +10329,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="255" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
         <v>20</v>
       </c>
@@ -10378,10 +10375,10 @@
         <v>128</v>
       </c>
       <c r="C256" t="s">
+        <v>266</v>
+      </c>
+      <c r="D256" t="s">
         <v>267</v>
-      </c>
-      <c r="D256" t="s">
-        <v>268</v>
       </c>
       <c r="E256" t="s">
         <v>27</v>
@@ -10396,7 +10393,7 @@
         <v>0</v>
       </c>
       <c r="I256" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J256" t="s">
         <v>20</v>
@@ -10416,10 +10413,10 @@
         <v>128</v>
       </c>
       <c r="C257" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D257" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E257" t="s">
         <v>27</v>
@@ -10434,7 +10431,7 @@
         <v>0</v>
       </c>
       <c r="I257" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J257" t="s">
         <v>20</v>
@@ -10454,10 +10451,10 @@
         <v>128</v>
       </c>
       <c r="C258" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D258" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E258" t="s">
         <v>27</v>
@@ -10472,7 +10469,7 @@
         <v>0</v>
       </c>
       <c r="I258" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J258" t="s">
         <v>20</v>
@@ -10492,10 +10489,10 @@
         <v>128</v>
       </c>
       <c r="C259" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D259" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E259" t="s">
         <v>27</v>
@@ -10510,7 +10507,7 @@
         <v>0</v>
       </c>
       <c r="I259" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J259" t="s">
         <v>20</v>
@@ -10530,10 +10527,10 @@
         <v>128</v>
       </c>
       <c r="C260" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D260" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E260" t="s">
         <v>27</v>
@@ -10548,7 +10545,7 @@
         <v>0</v>
       </c>
       <c r="I260" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J260" t="s">
         <v>20</v>
@@ -10568,10 +10565,10 @@
         <v>128</v>
       </c>
       <c r="C261" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D261" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E261" t="s">
         <v>27</v>
@@ -10606,10 +10603,10 @@
         <v>128</v>
       </c>
       <c r="C262" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D262" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E262" t="s">
         <v>27</v>
@@ -10688,10 +10685,10 @@
         <v>128</v>
       </c>
       <c r="C264" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D264" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E264" t="s">
         <v>20</v>
@@ -10732,10 +10729,10 @@
         <v>128</v>
       </c>
       <c r="C265" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D265" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E265" t="s">
         <v>20</v>
@@ -10776,10 +10773,10 @@
         <v>128</v>
       </c>
       <c r="C266" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D266" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E266" t="s">
         <v>20</v>
@@ -10820,10 +10817,10 @@
         <v>128</v>
       </c>
       <c r="C267" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D267" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E267" t="s">
         <v>20</v>
@@ -10856,7 +10853,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="268" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
         <v>20</v>
       </c>
@@ -10902,19 +10899,19 @@
         <v>128</v>
       </c>
       <c r="C269" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D269" t="s">
         <v>152</v>
       </c>
       <c r="E269" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F269" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="271" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
         <v>20</v>
       </c>
@@ -10960,10 +10957,10 @@
         <v>128</v>
       </c>
       <c r="C272" t="s">
+        <v>278</v>
+      </c>
+      <c r="D272" t="s">
         <v>279</v>
-      </c>
-      <c r="D272" t="s">
-        <v>280</v>
       </c>
       <c r="E272" t="s">
         <v>27</v>
@@ -10998,10 +10995,10 @@
         <v>128</v>
       </c>
       <c r="C273" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D273" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E273" t="s">
         <v>27</v>
@@ -11036,10 +11033,10 @@
         <v>128</v>
       </c>
       <c r="C274" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D274" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E274" t="s">
         <v>27</v>
@@ -11074,10 +11071,10 @@
         <v>128</v>
       </c>
       <c r="C275" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D275" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E275" t="s">
         <v>27</v>
@@ -11112,10 +11109,10 @@
         <v>128</v>
       </c>
       <c r="C276" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D276" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E276" t="s">
         <v>27</v>
@@ -11130,7 +11127,7 @@
         <v>1100</v>
       </c>
       <c r="I276" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J276" t="s">
         <v>20</v>
@@ -11150,10 +11147,10 @@
         <v>128</v>
       </c>
       <c r="C277" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D277" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E277" t="s">
         <v>27</v>
@@ -11168,7 +11165,7 @@
         <v>1100</v>
       </c>
       <c r="I277" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J277" t="s">
         <v>20</v>
@@ -11188,19 +11185,19 @@
         <v>128</v>
       </c>
       <c r="C278" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D278" t="s">
         <v>152</v>
       </c>
       <c r="E278" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F278" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="280" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
         <v>20</v>
       </c>
@@ -11246,7 +11243,7 @@
         <v>128</v>
       </c>
       <c r="C281" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D281" t="s">
         <v>93</v>
@@ -11284,10 +11281,10 @@
         <v>128</v>
       </c>
       <c r="C282" t="s">
+        <v>285</v>
+      </c>
+      <c r="D282" t="s">
         <v>286</v>
-      </c>
-      <c r="D282" t="s">
-        <v>287</v>
       </c>
       <c r="E282" t="s">
         <v>27</v>
@@ -11322,10 +11319,10 @@
         <v>128</v>
       </c>
       <c r="C283" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D283" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E283" t="s">
         <v>27</v>
@@ -11360,10 +11357,10 @@
         <v>128</v>
       </c>
       <c r="C284" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D284" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E284" t="s">
         <v>27</v>
@@ -11398,10 +11395,10 @@
         <v>128</v>
       </c>
       <c r="C285" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D285" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E285" t="s">
         <v>27</v>
@@ -11480,7 +11477,7 @@
         <v>128</v>
       </c>
       <c r="C287" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D287" t="s">
         <v>232</v>
@@ -11524,7 +11521,7 @@
         <v>128</v>
       </c>
       <c r="C288" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D288" t="s">
         <v>233</v>
@@ -11560,7 +11557,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="289" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
         <v>20</v>
       </c>
@@ -11606,7 +11603,7 @@
         <v>128</v>
       </c>
       <c r="C290" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D290" t="s">
         <v>152</v>
@@ -11670,7 +11667,7 @@
         <v>128</v>
       </c>
       <c r="C293" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D293" t="s">
         <v>58</v>
@@ -11706,7 +11703,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="294" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
         <v>20</v>
       </c>
@@ -11752,10 +11749,10 @@
         <v>128</v>
       </c>
       <c r="C295" t="s">
+        <v>290</v>
+      </c>
+      <c r="D295" t="s">
         <v>291</v>
-      </c>
-      <c r="D295" t="s">
-        <v>292</v>
       </c>
       <c r="E295" t="s">
         <v>19</v>
@@ -11790,10 +11787,10 @@
         <v>128</v>
       </c>
       <c r="C296" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D296" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E296" t="s">
         <v>19</v>
@@ -11828,10 +11825,10 @@
         <v>128</v>
       </c>
       <c r="C297" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D297" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E297" t="s">
         <v>27</v>
@@ -11866,10 +11863,10 @@
         <v>128</v>
       </c>
       <c r="C298" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D298" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E298" t="s">
         <v>27</v>
@@ -11904,10 +11901,10 @@
         <v>128</v>
       </c>
       <c r="C299" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D299" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E299" t="s">
         <v>27</v>
@@ -11986,10 +11983,10 @@
         <v>128</v>
       </c>
       <c r="C301" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D301" t="s">
-        <v>232</v>
+        <v>59</v>
       </c>
       <c r="E301" t="s">
         <v>20</v>
@@ -12022,7 +12019,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="302" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
         <v>20</v>
       </c>
@@ -12068,7 +12065,7 @@
         <v>128</v>
       </c>
       <c r="C303" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D303" t="s">
         <v>97</v>
@@ -12150,10 +12147,10 @@
         <v>128</v>
       </c>
       <c r="C305" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D305" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E305" t="s">
         <v>20</v>
@@ -12194,10 +12191,10 @@
         <v>128</v>
       </c>
       <c r="C306" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D306" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E306" t="s">
         <v>20</v>
@@ -12238,10 +12235,10 @@
         <v>128</v>
       </c>
       <c r="C307" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D307" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E307" t="s">
         <v>20</v>
@@ -12282,10 +12279,10 @@
         <v>128</v>
       </c>
       <c r="C308" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D308" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E308" t="s">
         <v>20</v>
@@ -12318,7 +12315,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="309" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
         <v>20</v>
       </c>
@@ -12364,7 +12361,7 @@
         <v>128</v>
       </c>
       <c r="C310" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D310" t="s">
         <v>152</v>
@@ -12376,7 +12373,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="312" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
         <v>20</v>
       </c>
@@ -12422,7 +12419,7 @@
         <v>128</v>
       </c>
       <c r="C313" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D313" t="s">
         <v>80</v>
@@ -12504,10 +12501,10 @@
         <v>128</v>
       </c>
       <c r="C315" t="s">
+        <v>300</v>
+      </c>
+      <c r="D315" t="s">
         <v>301</v>
-      </c>
-      <c r="D315" t="s">
-        <v>302</v>
       </c>
       <c r="E315" t="s">
         <v>20</v>
@@ -12548,10 +12545,10 @@
         <v>128</v>
       </c>
       <c r="C316" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D316" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E316" t="s">
         <v>20</v>
@@ -12592,10 +12589,10 @@
         <v>128</v>
       </c>
       <c r="C317" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D317" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E317" t="s">
         <v>20</v>
@@ -12636,10 +12633,10 @@
         <v>128</v>
       </c>
       <c r="C318" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D318" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E318" t="s">
         <v>20</v>
@@ -12680,10 +12677,10 @@
         <v>128</v>
       </c>
       <c r="C319" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D319" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E319" t="s">
         <v>20</v>
@@ -12724,10 +12721,10 @@
         <v>128</v>
       </c>
       <c r="C320" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D320" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E320" t="s">
         <v>20</v>
@@ -12760,7 +12757,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="321" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
         <v>20</v>
       </c>
@@ -12806,7 +12803,7 @@
         <v>128</v>
       </c>
       <c r="C322" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D322" t="s">
         <v>152</v>
@@ -12818,56 +12815,56 @@
         <v>27</v>
       </c>
     </row>
-    <row r="324" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B324" s="2" t="s">
         <v>308</v>
-      </c>
-      <c r="B324" s="2" t="s">
-        <v>309</v>
       </c>
       <c r="C324" t="s">
         <v>2</v>
       </c>
       <c r="D324" t="s">
+        <v>309</v>
+      </c>
+      <c r="E324" t="s">
         <v>310</v>
       </c>
-      <c r="E324" t="s">
+      <c r="F324" t="s">
         <v>311</v>
       </c>
-      <c r="F324" t="s">
+      <c r="G324" t="s">
         <v>312</v>
       </c>
-      <c r="G324" t="s">
+      <c r="H324" t="s">
         <v>313</v>
       </c>
-      <c r="H324" t="s">
+      <c r="I324" t="s">
         <v>314</v>
       </c>
-      <c r="I324" t="s">
+      <c r="J324" t="s">
         <v>315</v>
       </c>
-      <c r="J324" t="s">
+      <c r="K324" t="s">
         <v>316</v>
       </c>
-      <c r="K324" t="s">
+    </row>
+    <row r="325" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A325" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B325" s="3" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="325" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A325" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B325" s="3" t="s">
+      <c r="C325" t="s">
         <v>318</v>
-      </c>
-      <c r="C325" t="s">
-        <v>319</v>
       </c>
       <c r="D325" t="s">
         <v>153</v>
       </c>
       <c r="E325" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F325">
         <v>0</v>
@@ -12879,21 +12876,21 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="327" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B327" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C327" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D327" t="s">
         <v>129</v>
       </c>
       <c r="E327" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F327">
         <v>-800</v>
@@ -12905,21 +12902,21 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B328" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C328" t="s">
+        <v>320</v>
+      </c>
+      <c r="D328" t="s">
+        <v>320</v>
+      </c>
+      <c r="E328" t="s">
         <v>321</v>
-      </c>
-      <c r="D328" t="s">
-        <v>321</v>
-      </c>
-      <c r="E328" t="s">
-        <v>322</v>
       </c>
       <c r="F328">
         <v>0</v>
@@ -12934,21 +12931,21 @@
         <v>14</v>
       </c>
     </row>
-    <row r="330" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B330" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C330" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D330" t="s">
         <v>188</v>
       </c>
       <c r="E330" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F330">
         <v>0</v>
@@ -12960,21 +12957,21 @@
         <v>37060</v>
       </c>
     </row>
-    <row r="331" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B331" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C331" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D331" t="s">
         <v>192</v>
       </c>
       <c r="E331" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F331">
         <v>-800</v>
@@ -12986,21 +12983,21 @@
         <v>37370</v>
       </c>
     </row>
-    <row r="332" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B332" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C332" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D332" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E332" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F332">
         <v>2400</v>
@@ -13012,21 +13009,21 @@
         <v>35060</v>
       </c>
     </row>
-    <row r="334" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B334" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C334" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D334" t="s">
         <v>235</v>
       </c>
       <c r="E334" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F334">
         <v>1900</v>
@@ -13038,21 +13035,21 @@
         <v>38140</v>
       </c>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B335" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C335" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D335" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E335" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F335">
         <v>3000</v>
@@ -13067,21 +13064,21 @@
         <v>14</v>
       </c>
     </row>
-    <row r="336" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B336" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C336" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D336" t="s">
         <v>242</v>
       </c>
       <c r="E336" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F336">
         <v>46990</v>
@@ -13093,21 +13090,21 @@
         <v>38140</v>
       </c>
     </row>
-    <row r="338" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B338" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C338" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D338" t="s">
         <v>243</v>
       </c>
       <c r="E338" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F338">
         <v>-1900</v>
@@ -13128,21 +13125,21 @@
         <v>180</v>
       </c>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B339" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C339" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D339" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E339" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F339">
         <v>-2600</v>
@@ -13157,21 +13154,21 @@
         <v>4</v>
       </c>
     </row>
-    <row r="340" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B340" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C340" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D340" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E340" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F340">
         <v>-7800</v>
@@ -13183,21 +13180,21 @@
         <v>39470</v>
       </c>
     </row>
-    <row r="341" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B341" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C341" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D341" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E341" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F341">
         <v>-13900</v>
@@ -13209,21 +13206,21 @@
         <v>36540</v>
       </c>
     </row>
-    <row r="343" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B343" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C343" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D343" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E343" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F343">
         <v>0</v>
@@ -13235,21 +13232,21 @@
         <v>47520</v>
       </c>
     </row>
-    <row r="345" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B345" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C345" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D345" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E345" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F345">
         <v>30000</v>
@@ -13261,21 +13258,21 @@
         <v>40020</v>
       </c>
     </row>
-    <row r="346" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B346" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C346" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D346" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E346" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F346">
         <v>30000</v>
@@ -13287,16 +13284,16 @@
         <v>14000</v>
       </c>
     </row>
-    <row r="347" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B347" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/plate3d/PLATE3D_TOWER.xlsx
+++ b/plate3d/PLATE3D_TOWER.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2476" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2488" uniqueCount="390">
   <si>
     <t>TOWER CRANE</t>
   </si>
@@ -1158,6 +1158,30 @@
   </si>
   <si>
     <t>as.hoist</t>
+  </si>
+  <si>
+    <t>VIEW</t>
+  </si>
+  <si>
+    <t>ISO</t>
+  </si>
+  <si>
+    <t>TOWER - ISOMETRIC</t>
+  </si>
+  <si>
+    <t>PLOT</t>
+  </si>
+  <si>
+    <t>PART</t>
+  </si>
+  <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>PLATES</t>
+  </si>
+  <si>
+    <t>SECTIONS</t>
   </si>
   <si>
     <t>END</t>
@@ -2206,14 +2230,14 @@
     <mergeCell ref="B26:J26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N347"/>
+  <dimension ref="A1:N350"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="58" customWidth="1"/>
@@ -2564,6 +2588,7 @@
         <v>16</v>
       </c>
     </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>4</v>
@@ -3047,6 +3072,7 @@
         <v>1300</v>
       </c>
     </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="15" t="s">
         <v>4</v>
@@ -3793,6 +3819,7 @@
         <v>325</v>
       </c>
     </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="15" t="s">
         <v>4</v>
@@ -3913,6 +3940,7 @@
         <v>130</v>
       </c>
     </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="15" t="s">
         <v>160</v>
@@ -4120,6 +4148,7 @@
         <v>159</v>
       </c>
     </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="15" t="s">
         <v>4</v>
@@ -4994,6 +5023,7 @@
         <v>74</v>
       </c>
     </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" s="15" t="s">
         <v>4</v>
@@ -6642,6 +6672,7 @@
         <v>208</v>
       </c>
     </row>
+    <row r="138" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A139" s="15" t="s">
         <v>4</v>
@@ -7022,6 +7053,7 @@
         <v>243</v>
       </c>
     </row>
+    <row r="149" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="150" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A150" s="15" t="s">
         <v>4</v>
@@ -9031,6 +9063,7 @@
         <v>74</v>
       </c>
     </row>
+    <row r="196" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="197" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A197" s="15" t="s">
         <v>4</v>
@@ -9541,6 +9574,7 @@
         <v>81</v>
       </c>
     </row>
+    <row r="209" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="210" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A210" s="15" t="s">
         <v>4</v>
@@ -9868,6 +9902,7 @@
         <v>81</v>
       </c>
     </row>
+    <row r="218" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="219" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A219" s="15" t="s">
         <v>4</v>
@@ -10333,6 +10368,7 @@
         <v>81</v>
       </c>
     </row>
+    <row r="230" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="231" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A231" s="15" t="s">
         <v>4</v>
@@ -11279,6 +11315,7 @@
         <v>208</v>
       </c>
     </row>
+    <row r="254" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="255" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A255" s="15" t="s">
         <v>4</v>
@@ -11861,6 +11898,7 @@
         <v>81</v>
       </c>
     </row>
+    <row r="270" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="271" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A271" s="15" t="s">
         <v>4</v>
@@ -12147,6 +12185,7 @@
         <v>81</v>
       </c>
     </row>
+    <row r="279" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="280" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A280" s="15" t="s">
         <v>4</v>
@@ -12565,6 +12604,7 @@
         <v>81</v>
       </c>
     </row>
+    <row r="291" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="292" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A292" s="15" t="s">
         <v>4</v>
@@ -13327,6 +13367,7 @@
         <v>81</v>
       </c>
     </row>
+    <row r="311" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="312" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A312" s="15" t="s">
         <v>4</v>
@@ -13785,6 +13826,7 @@
         <v>81</v>
       </c>
     </row>
+    <row r="323" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="324" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A324" s="15" t="s">
         <v>361</v>
@@ -13847,6 +13889,7 @@
         <v>1000</v>
       </c>
     </row>
+    <row r="326" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="327" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A327" s="15" t="s">
         <v>4</v>
@@ -13905,6 +13948,7 @@
         <v>14</v>
       </c>
     </row>
+    <row r="329" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="330" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A330" s="15" t="s">
         <v>4</v>
@@ -14020,6 +14064,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="333" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="334" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A334" s="15" t="s">
         <v>4</v>
@@ -14130,6 +14175,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="337" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="338" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A338" s="15" t="s">
         <v>4</v>
@@ -14279,6 +14325,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="342" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="343" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A343" s="15" t="s">
         <v>4</v>
@@ -14316,6 +14363,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="344" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="345" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A345" s="15" t="s">
         <v>4</v>
@@ -14394,16 +14442,67 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A347" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="B347" s="17" t="s">
+    <row r="347" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B347" t="s">
         <v>381</v>
+      </c>
+      <c r="C347" t="s">
+        <v>372</v>
+      </c>
+      <c r="D347" t="s">
+        <v>382</v>
+      </c>
+      <c r="G347">
+        <v>50</v>
+      </c>
+      <c r="H347" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="348" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B348" t="s">
+        <v>384</v>
+      </c>
+      <c r="C348" t="s">
+        <v>385</v>
+      </c>
+      <c r="D348" t="s">
+        <v>386</v>
+      </c>
+      <c r="E348">
+        <v>10</v>
+      </c>
+      <c r="F348" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="349" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B349" t="s">
+        <v>384</v>
+      </c>
+      <c r="C349" t="s">
+        <v>70</v>
+      </c>
+      <c r="D349" t="s">
+        <v>386</v>
+      </c>
+      <c r="E349">
+        <v>20</v>
+      </c>
+      <c r="F349" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A350" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B350" s="17" t="s">
+        <v>389</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/plate3d/PLATE3D_TOWER.xlsx
+++ b/plate3d/PLATE3D_TOWER.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2488" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2476" uniqueCount="382">
   <si>
     <t>TOWER CRANE</t>
   </si>
@@ -1158,30 +1158,6 @@
   </si>
   <si>
     <t>as.hoist</t>
-  </si>
-  <si>
-    <t>VIEW</t>
-  </si>
-  <si>
-    <t>ISO</t>
-  </si>
-  <si>
-    <t>TOWER - ISOMETRIC</t>
-  </si>
-  <si>
-    <t>PLOT</t>
-  </si>
-  <si>
-    <t>PART</t>
-  </si>
-  <si>
-    <t>ALL</t>
-  </si>
-  <si>
-    <t>PLATES</t>
-  </si>
-  <si>
-    <t>SECTIONS</t>
   </si>
   <si>
     <t>END</t>
@@ -2230,14 +2206,14 @@
     <mergeCell ref="B26:J26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N350"/>
+  <dimension ref="A1:N347"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="58" customWidth="1"/>
@@ -2588,7 +2564,6 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>4</v>
@@ -3072,7 +3047,6 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="15" t="s">
         <v>4</v>
@@ -3819,7 +3793,6 @@
         <v>325</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="15" t="s">
         <v>4</v>
@@ -3940,7 +3913,6 @@
         <v>130</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="15" t="s">
         <v>160</v>
@@ -4148,7 +4120,6 @@
         <v>159</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="15" t="s">
         <v>4</v>
@@ -5023,7 +4994,6 @@
         <v>74</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" s="15" t="s">
         <v>4</v>
@@ -6672,7 +6642,6 @@
         <v>208</v>
       </c>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A139" s="15" t="s">
         <v>4</v>
@@ -7053,7 +7022,6 @@
         <v>243</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="150" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A150" s="15" t="s">
         <v>4</v>
@@ -9063,7 +9031,6 @@
         <v>74</v>
       </c>
     </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="197" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A197" s="15" t="s">
         <v>4</v>
@@ -9574,7 +9541,6 @@
         <v>81</v>
       </c>
     </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="210" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A210" s="15" t="s">
         <v>4</v>
@@ -9902,7 +9868,6 @@
         <v>81</v>
       </c>
     </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="219" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A219" s="15" t="s">
         <v>4</v>
@@ -10368,7 +10333,6 @@
         <v>81</v>
       </c>
     </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="231" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A231" s="15" t="s">
         <v>4</v>
@@ -11315,7 +11279,6 @@
         <v>208</v>
       </c>
     </row>
-    <row r="254" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="255" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A255" s="15" t="s">
         <v>4</v>
@@ -11898,7 +11861,6 @@
         <v>81</v>
       </c>
     </row>
-    <row r="270" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="271" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A271" s="15" t="s">
         <v>4</v>
@@ -12185,7 +12147,6 @@
         <v>81</v>
       </c>
     </row>
-    <row r="279" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="280" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A280" s="15" t="s">
         <v>4</v>
@@ -12604,7 +12565,6 @@
         <v>81</v>
       </c>
     </row>
-    <row r="291" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="292" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A292" s="15" t="s">
         <v>4</v>
@@ -13367,7 +13327,6 @@
         <v>81</v>
       </c>
     </row>
-    <row r="311" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="312" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A312" s="15" t="s">
         <v>4</v>
@@ -13826,7 +13785,6 @@
         <v>81</v>
       </c>
     </row>
-    <row r="323" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="324" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A324" s="15" t="s">
         <v>361</v>
@@ -13889,7 +13847,6 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="326" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="327" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A327" s="15" t="s">
         <v>4</v>
@@ -13948,7 +13905,6 @@
         <v>14</v>
       </c>
     </row>
-    <row r="329" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="330" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A330" s="15" t="s">
         <v>4</v>
@@ -14064,7 +14020,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="334" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A334" s="15" t="s">
         <v>4</v>
@@ -14175,7 +14130,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="338" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A338" s="15" t="s">
         <v>4</v>
@@ -14325,7 +14279,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="343" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A343" s="15" t="s">
         <v>4</v>
@@ -14363,7 +14316,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="345" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A345" s="15" t="s">
         <v>4</v>
@@ -14442,67 +14394,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B347" t="s">
+    <row r="347" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A347" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B347" s="17" t="s">
         <v>381</v>
-      </c>
-      <c r="C347" t="s">
-        <v>372</v>
-      </c>
-      <c r="D347" t="s">
-        <v>382</v>
-      </c>
-      <c r="G347">
-        <v>50</v>
-      </c>
-      <c r="H347" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="348" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B348" t="s">
-        <v>384</v>
-      </c>
-      <c r="C348" t="s">
-        <v>385</v>
-      </c>
-      <c r="D348" t="s">
-        <v>386</v>
-      </c>
-      <c r="E348">
-        <v>10</v>
-      </c>
-      <c r="F348" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="349" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B349" t="s">
-        <v>384</v>
-      </c>
-      <c r="C349" t="s">
-        <v>70</v>
-      </c>
-      <c r="D349" t="s">
-        <v>386</v>
-      </c>
-      <c r="E349">
-        <v>20</v>
-      </c>
-      <c r="F349" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="350" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A350" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="B350" s="17" t="s">
-        <v>389</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>